--- a/outputs/daily/hr_rankings_2026-08-04.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-04.xlsx
@@ -65295,27 +65295,27 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>676609</t>
+          <t>693304</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Jose Caballero</t>
+          <t>Nick Gonzales</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>2026-08-04T23:05:00Z</t>
+          <t>2026-08-04T23:40:00Z</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
@@ -65325,17 +65325,17 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>Hunter Dobbins</t>
+          <t>Logan Henderson</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>690928</t>
+          <t>701656</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
@@ -65358,26 +65358,26 @@
       </c>
       <c r="O238" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P238" t="n">
-        <v>9.300000000000001</v>
+        <v>16.5</v>
       </c>
       <c r="Q238" t="n">
-        <v>35.3</v>
+        <v>29.4</v>
       </c>
       <c r="R238" t="n">
-        <v>38.2</v>
+        <v>27.6</v>
       </c>
       <c r="S238" t="n">
-        <v>47.9</v>
+        <v>71.7</v>
       </c>
       <c r="T238" t="n">
         <v>50</v>
       </c>
       <c r="U238" t="n">
-        <v>71.2</v>
+        <v>17</v>
       </c>
       <c r="V238" t="inlineStr">
         <is>
@@ -65391,7 +65391,7 @@
       </c>
       <c r="X238" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y238" t="inlineStr">
@@ -65438,22 +65438,22 @@
       </c>
       <c r="AI238" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AJ238" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK238" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 7/30, 0 HR</t>
         </is>
       </c>
       <c r="AL238" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.0% barrel, 4.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.9% barrel, 4.4 HR allowed</t>
         </is>
       </c>
       <c r="AM238" t="inlineStr">
@@ -65463,104 +65463,104 @@
       </c>
       <c r="AN238" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AO238" t="inlineStr">
         <is>
-          <t>26.61</t>
+          <t>36.56</t>
         </is>
       </c>
       <c r="AP238" t="inlineStr">
         <is>
-          <t>84.53</t>
+          <t>86.91</t>
         </is>
       </c>
       <c r="AQ238" t="inlineStr">
         <is>
-          <t>96.3907</t>
+          <t>98.2823</t>
         </is>
       </c>
       <c r="AR238" t="inlineStr">
         <is>
-          <t>0.3411</t>
+          <t>0.3813</t>
         </is>
       </c>
       <c r="AS238" t="inlineStr">
         <is>
-          <t>0.1136</t>
+          <t>0.1077</t>
         </is>
       </c>
       <c r="AT238" t="inlineStr">
         <is>
-          <t>0.2857</t>
+          <t>0.312</t>
         </is>
       </c>
       <c r="AU238" t="inlineStr">
         <is>
-          <t>68.75</t>
+          <t>70.64</t>
         </is>
       </c>
       <c r="AV238" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>12.8</t>
         </is>
       </c>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>38.48</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>21.31</t>
+          <t>20.91</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="AZ238" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>0.095</t>
         </is>
       </c>
       <c r="BA238" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="BB238" t="inlineStr">
         <is>
-          <t>43.59</t>
+          <t>33.85</t>
         </is>
       </c>
       <c r="BC238" t="inlineStr">
         <is>
-          <t>89.37</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD238" t="inlineStr">
         <is>
-          <t>0.3842</t>
+          <t>0.3443</t>
         </is>
       </c>
       <c r="BE238" t="inlineStr">
         <is>
-          <t>0.1425</t>
+          <t>0.1316</t>
         </is>
       </c>
       <c r="BF238" t="inlineStr">
         <is>
-          <t>22.88</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BG238" t="inlineStr"/>
       <c r="BH238" t="inlineStr"/>
       <c r="BI238" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ238" t="inlineStr"/>
@@ -65571,27 +65571,27 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>693304</t>
+          <t>685133</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Nick Gonzales</t>
+          <t>Wade Meckler</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>2026-08-04T23:40:00Z</t>
+          <t>2026-08-04T22:35:00Z</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
@@ -65601,26 +65601,14 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I239" t="inlineStr">
-        <is>
-          <t>Logan Henderson</t>
-        </is>
-      </c>
-      <c r="J239" t="inlineStr">
-        <is>
-          <t>701656</t>
-        </is>
-      </c>
-      <c r="K239" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr"/>
+      <c r="J239" t="inlineStr"/>
+      <c r="K239" t="inlineStr"/>
       <c r="L239" t="n">
-        <v>32</v>
+        <v>31.8</v>
       </c>
       <c r="M239" t="inlineStr">
         <is>
@@ -65638,22 +65626,22 @@
         </is>
       </c>
       <c r="P239" t="n">
-        <v>16.5</v>
+        <v>14.3</v>
       </c>
       <c r="Q239" t="n">
-        <v>29.4</v>
+        <v>41.2</v>
       </c>
       <c r="R239" t="n">
-        <v>27.6</v>
+        <v>32.1</v>
       </c>
       <c r="S239" t="n">
-        <v>71.7</v>
+        <v>40.2</v>
       </c>
       <c r="T239" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="U239" t="n">
-        <v>17</v>
+        <v>26.8</v>
       </c>
       <c r="V239" t="inlineStr">
         <is>
@@ -65667,7 +65655,7 @@
       </c>
       <c r="X239" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y239" t="inlineStr">
@@ -65692,7 +65680,7 @@
       </c>
       <c r="AC239" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:</t>
         </is>
       </c>
       <c r="AD239" t="inlineStr"/>
@@ -65709,27 +65697,27 @@
       </c>
       <c r="AH239" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI239" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/30, 0 HR</t>
+          <t>Last 7 games: 3/17, 1 HR</t>
         </is>
       </c>
       <c r="AL239" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.9% barrel, 4.4 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM239" t="inlineStr">
@@ -65739,104 +65727,80 @@
       </c>
       <c r="AN239" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AO239" t="inlineStr">
         <is>
-          <t>36.56</t>
+          <t>31.3</t>
         </is>
       </c>
       <c r="AP239" t="inlineStr">
         <is>
-          <t>86.91</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AQ239" t="inlineStr">
         <is>
-          <t>98.2823</t>
+          <t>96.4218</t>
         </is>
       </c>
       <c r="AR239" t="inlineStr">
         <is>
-          <t>0.3813</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AS239" t="inlineStr">
         <is>
-          <t>0.1077</t>
+          <t>0.118</t>
         </is>
       </c>
       <c r="AT239" t="inlineStr">
         <is>
-          <t>0.312</t>
+          <t>0.318</t>
         </is>
       </c>
       <c r="AU239" t="inlineStr">
         <is>
-          <t>70.64</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="AV239" t="inlineStr">
         <is>
-          <t>12.8</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>38.48</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>20.91</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ239" t="inlineStr">
         <is>
-          <t>0.095</t>
-        </is>
-      </c>
-      <c r="BA239" t="inlineStr">
-        <is>
-          <t>7.9</t>
-        </is>
-      </c>
-      <c r="BB239" t="inlineStr">
-        <is>
-          <t>33.85</t>
-        </is>
-      </c>
-      <c r="BC239" t="inlineStr">
-        <is>
-          <t>87.75</t>
-        </is>
-      </c>
-      <c r="BD239" t="inlineStr">
-        <is>
-          <t>0.3443</t>
-        </is>
-      </c>
-      <c r="BE239" t="inlineStr">
-        <is>
-          <t>0.1316</t>
-        </is>
-      </c>
-      <c r="BF239" t="inlineStr">
-        <is>
-          <t>29.67</t>
-        </is>
-      </c>
+          <t>0.121</t>
+        </is>
+      </c>
+      <c r="BA239" t="inlineStr"/>
+      <c r="BB239" t="inlineStr"/>
+      <c r="BC239" t="inlineStr"/>
+      <c r="BD239" t="inlineStr"/>
+      <c r="BE239" t="inlineStr"/>
+      <c r="BF239" t="inlineStr"/>
       <c r="BG239" t="inlineStr"/>
       <c r="BH239" t="inlineStr"/>
       <c r="BI239" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ239" t="inlineStr"/>
@@ -65847,27 +65811,27 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>685133</t>
+          <t>695731</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Wade Meckler</t>
+          <t>Braden Montgomery</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>2026-08-04T22:35:00Z</t>
+          <t>2026-08-04T23:10:00Z</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
@@ -65877,12 +65841,24 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I240" t="inlineStr"/>
-      <c r="J240" t="inlineStr"/>
-      <c r="K240" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>Patrick Sandoval</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>663776</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L240" t="n">
         <v>31.8</v>
       </c>
@@ -65898,26 +65874,26 @@
       </c>
       <c r="O240" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P240" t="n">
-        <v>14.3</v>
+        <v>20.5</v>
       </c>
       <c r="Q240" t="n">
-        <v>41.2</v>
+        <v>21.9</v>
       </c>
       <c r="R240" t="n">
-        <v>32.1</v>
+        <v>28.7</v>
       </c>
       <c r="S240" t="n">
-        <v>40.2</v>
+        <v>59.8</v>
       </c>
       <c r="T240" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="U240" t="n">
-        <v>26.8</v>
+        <v>8.1</v>
       </c>
       <c r="V240" t="inlineStr">
         <is>
@@ -65931,7 +65907,7 @@
       </c>
       <c r="X240" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y240" t="inlineStr">
@@ -65956,7 +65932,7 @@
       </c>
       <c r="AC240" t="inlineStr">
         <is>
-          <t>H:2026 P:</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AD240" t="inlineStr"/>
@@ -65973,27 +65949,27 @@
       </c>
       <c r="AH240" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI240" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ240" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK240" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/17, 1 HR</t>
+          <t>Last 7 games: 4/23, 0 HR</t>
         </is>
       </c>
       <c r="AL240" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 5.1% barrel, 3.0 HR allowed</t>
         </is>
       </c>
       <c r="AM240" t="inlineStr">
@@ -66003,57 +65979,57 @@
       </c>
       <c r="AN240" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="AO240" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="AP240" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AQ240" t="inlineStr">
         <is>
-          <t>96.4218</t>
+          <t>99.9903</t>
         </is>
       </c>
       <c r="AR240" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.361</t>
         </is>
       </c>
       <c r="AS240" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>0.114</t>
         </is>
       </c>
       <c r="AT240" t="inlineStr">
         <is>
-          <t>0.318</t>
+          <t>0.306</t>
         </is>
       </c>
       <c r="AU240" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>69.6</t>
         </is>
       </c>
       <c r="AV240" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr">
@@ -66063,20 +66039,44 @@
       </c>
       <c r="AZ240" t="inlineStr">
         <is>
-          <t>0.121</t>
-        </is>
-      </c>
-      <c r="BA240" t="inlineStr"/>
-      <c r="BB240" t="inlineStr"/>
-      <c r="BC240" t="inlineStr"/>
-      <c r="BD240" t="inlineStr"/>
-      <c r="BE240" t="inlineStr"/>
-      <c r="BF240" t="inlineStr"/>
+          <t>0.145</t>
+        </is>
+      </c>
+      <c r="BA240" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="BB240" t="inlineStr">
+        <is>
+          <t>35.6</t>
+        </is>
+      </c>
+      <c r="BC240" t="inlineStr">
+        <is>
+          <t>86.5</t>
+        </is>
+      </c>
+      <c r="BD240" t="inlineStr">
+        <is>
+          <t>0.406</t>
+        </is>
+      </c>
+      <c r="BE240" t="inlineStr">
+        <is>
+          <t>0.136</t>
+        </is>
+      </c>
+      <c r="BF240" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
+      </c>
       <c r="BG240" t="inlineStr"/>
       <c r="BH240" t="inlineStr"/>
       <c r="BI240" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Fenway Park</t>
         </is>
       </c>
       <c r="BJ240" t="inlineStr"/>
@@ -66087,27 +66087,27 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>695731</t>
+          <t>677587</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Braden Montgomery</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>2026-08-04T23:10:00Z</t>
+          <t>2026-08-04T22:40:00Z</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
@@ -66117,17 +66117,17 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>Patrick Sandoval</t>
+          <t>Sean Manaea</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>663776</t>
+          <t>640455</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
@@ -66136,7 +66136,7 @@
         </is>
       </c>
       <c r="L241" t="n">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="M241" t="inlineStr">
         <is>
@@ -66154,22 +66154,22 @@
         </is>
       </c>
       <c r="P241" t="n">
-        <v>20.5</v>
+        <v>13.7</v>
       </c>
       <c r="Q241" t="n">
-        <v>21.9</v>
+        <v>44.4</v>
       </c>
       <c r="R241" t="n">
-        <v>28.7</v>
+        <v>27.6</v>
       </c>
       <c r="S241" t="n">
-        <v>59.8</v>
+        <v>40.2</v>
       </c>
       <c r="T241" t="n">
         <v>75</v>
       </c>
       <c r="U241" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="V241" t="inlineStr">
         <is>
@@ -66183,7 +66183,7 @@
       </c>
       <c r="X241" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y241" t="inlineStr">
@@ -66208,7 +66208,7 @@
       </c>
       <c r="AC241" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD241" t="inlineStr"/>
@@ -66225,12 +66225,12 @@
       </c>
       <c r="AH241" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI241" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ241" t="inlineStr">
@@ -66240,12 +66240,12 @@
       </c>
       <c r="AK241" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/23, 0 HR</t>
+          <t>Last 7 games: 2/26, 0 HR</t>
         </is>
       </c>
       <c r="AL241" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 5.1% barrel, 3.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.1% barrel, 13.0 HR allowed</t>
         </is>
       </c>
       <c r="AM241" t="inlineStr">
@@ -66255,104 +66255,104 @@
       </c>
       <c r="AN241" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="AO241" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>32.56</t>
         </is>
       </c>
       <c r="AP241" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>86.95</t>
         </is>
       </c>
       <c r="AQ241" t="inlineStr">
         <is>
-          <t>99.9903</t>
+          <t>97.3755</t>
         </is>
       </c>
       <c r="AR241" t="inlineStr">
         <is>
-          <t>0.361</t>
+          <t>0.3503</t>
         </is>
       </c>
       <c r="AS241" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>0.1053</t>
         </is>
       </c>
       <c r="AT241" t="inlineStr">
         <is>
-          <t>0.306</t>
+          <t>0.2929</t>
         </is>
       </c>
       <c r="AU241" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>70.07</t>
         </is>
       </c>
       <c r="AV241" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>7.36</t>
         </is>
       </c>
       <c r="AW241" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>43.78</t>
         </is>
       </c>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>24.67</t>
         </is>
       </c>
       <c r="AY241" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="AZ241" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>0.1196</t>
         </is>
       </c>
       <c r="BA241" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>9.11</t>
         </is>
       </c>
       <c r="BB241" t="inlineStr">
         <is>
-          <t>35.6</t>
+          <t>41.27</t>
         </is>
       </c>
       <c r="BC241" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>88.89</t>
         </is>
       </c>
       <c r="BD241" t="inlineStr">
         <is>
-          <t>0.406</t>
+          <t>0.4185</t>
         </is>
       </c>
       <c r="BE241" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>0.1701</t>
         </is>
       </c>
       <c r="BF241" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="BG241" t="inlineStr"/>
       <c r="BH241" t="inlineStr"/>
       <c r="BI241" t="inlineStr">
         <is>
-          <t>Fenway Park</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ241" t="inlineStr"/>
@@ -66363,27 +66363,27 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>677587</t>
+          <t>687551</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Drew Gilbert</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>2026-08-04T22:40:00Z</t>
+          <t>2026-08-05T00:05:00Z</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
@@ -66398,12 +66398,12 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>Sean Manaea</t>
+          <t>MacKenzie Gore</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>640455</t>
+          <t>669022</t>
         </is>
       </c>
       <c r="K242" t="inlineStr">
@@ -66412,7 +66412,7 @@
         </is>
       </c>
       <c r="L242" t="n">
-        <v>31.7</v>
+        <v>31.4</v>
       </c>
       <c r="M242" t="inlineStr">
         <is>
@@ -66426,14 +66426,14 @@
       </c>
       <c r="O242" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P242" t="n">
-        <v>13.7</v>
+        <v>13.1</v>
       </c>
       <c r="Q242" t="n">
-        <v>44.4</v>
+        <v>47.8</v>
       </c>
       <c r="R242" t="n">
         <v>27.6</v>
@@ -66442,10 +66442,10 @@
         <v>40.2</v>
       </c>
       <c r="T242" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U242" t="n">
-        <v>0</v>
+        <v>26.1</v>
       </c>
       <c r="V242" t="inlineStr">
         <is>
@@ -66501,12 +66501,12 @@
       </c>
       <c r="AH242" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI242" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ242" t="inlineStr">
@@ -66516,12 +66516,12 @@
       </c>
       <c r="AK242" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/26, 0 HR</t>
+          <t>Last 7 games: 5/17, 0 HR</t>
         </is>
       </c>
       <c r="AL242" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.1% barrel, 13.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.6% barrel, 17.2 HR allowed</t>
         </is>
       </c>
       <c r="AM242" t="inlineStr">
@@ -66531,104 +66531,104 @@
       </c>
       <c r="AN242" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AO242" t="inlineStr">
         <is>
-          <t>32.56</t>
+          <t>34.33</t>
         </is>
       </c>
       <c r="AP242" t="inlineStr">
         <is>
-          <t>86.95</t>
+          <t>86.32</t>
         </is>
       </c>
       <c r="AQ242" t="inlineStr">
         <is>
-          <t>97.3755</t>
+          <t>97.7341</t>
         </is>
       </c>
       <c r="AR242" t="inlineStr">
         <is>
-          <t>0.3503</t>
+          <t>0.3472</t>
         </is>
       </c>
       <c r="AS242" t="inlineStr">
         <is>
-          <t>0.1053</t>
+          <t>0.1034</t>
         </is>
       </c>
       <c r="AT242" t="inlineStr">
         <is>
-          <t>0.2929</t>
+          <t>0.2973</t>
         </is>
       </c>
       <c r="AU242" t="inlineStr">
         <is>
-          <t>70.07</t>
+          <t>70.52</t>
         </is>
       </c>
       <c r="AV242" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>43.78</t>
+          <t>40.56</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>24.67</t>
+          <t>18.78</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AZ242" t="inlineStr">
         <is>
-          <t>0.1196</t>
+          <t>0.1271</t>
         </is>
       </c>
       <c r="BA242" t="inlineStr">
         <is>
-          <t>9.11</t>
+          <t>9.62</t>
         </is>
       </c>
       <c r="BB242" t="inlineStr">
         <is>
-          <t>41.27</t>
+          <t>42.91</t>
         </is>
       </c>
       <c r="BC242" t="inlineStr">
         <is>
-          <t>88.89</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="BD242" t="inlineStr">
         <is>
-          <t>0.4185</t>
+          <t>0.3912</t>
         </is>
       </c>
       <c r="BE242" t="inlineStr">
         <is>
-          <t>0.1701</t>
+          <t>0.1558</t>
         </is>
       </c>
       <c r="BF242" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>27.93</t>
         </is>
       </c>
       <c r="BG242" t="inlineStr"/>
       <c r="BH242" t="inlineStr"/>
       <c r="BI242" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ242" t="inlineStr"/>
@@ -66639,24 +66639,24 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>687551</t>
+          <t>677649</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Drew Gilbert</t>
+          <t>Ezequiel Duran</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
+          <t>TEX</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="E243" t="inlineStr">
-        <is>
-          <t>TEX</t>
-        </is>
-      </c>
       <c r="F243" t="inlineStr">
         <is>
           <t>2026-08-05T00:05:00Z</t>
@@ -66669,26 +66669,26 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>MacKenzie Gore</t>
+          <t>Blade Tidwell</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>669022</t>
+          <t>694918</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L243" t="n">
-        <v>31.4</v>
+        <v>31.1</v>
       </c>
       <c r="M243" t="inlineStr">
         <is>
@@ -66706,22 +66706,22 @@
         </is>
       </c>
       <c r="P243" t="n">
-        <v>13.1</v>
+        <v>20.3</v>
       </c>
       <c r="Q243" t="n">
-        <v>47.8</v>
+        <v>21.9</v>
       </c>
       <c r="R243" t="n">
         <v>27.6</v>
       </c>
       <c r="S243" t="n">
-        <v>40.2</v>
+        <v>59.8</v>
       </c>
       <c r="T243" t="n">
         <v>50</v>
       </c>
       <c r="U243" t="n">
-        <v>26.1</v>
+        <v>42.3</v>
       </c>
       <c r="V243" t="inlineStr">
         <is>
@@ -66735,7 +66735,7 @@
       </c>
       <c r="X243" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y243" t="inlineStr">
@@ -66777,27 +66777,27 @@
       </c>
       <c r="AH243" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI243" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/17, 0 HR</t>
+          <t>Last 7 games: 7/25, 1 HR</t>
         </is>
       </c>
       <c r="AL243" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.6% barrel, 17.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.4% barrel, 1.9 HR allowed</t>
         </is>
       </c>
       <c r="AM243" t="inlineStr">
@@ -66807,97 +66807,97 @@
       </c>
       <c r="AN243" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>5.47</t>
         </is>
       </c>
       <c r="AO243" t="inlineStr">
         <is>
-          <t>34.33</t>
+          <t>33.91</t>
         </is>
       </c>
       <c r="AP243" t="inlineStr">
         <is>
-          <t>86.32</t>
+          <t>87.61</t>
         </is>
       </c>
       <c r="AQ243" t="inlineStr">
         <is>
-          <t>97.7341</t>
+          <t>98.6051</t>
         </is>
       </c>
       <c r="AR243" t="inlineStr">
         <is>
-          <t>0.3472</t>
+          <t>0.3608</t>
         </is>
       </c>
       <c r="AS243" t="inlineStr">
         <is>
-          <t>0.1034</t>
+          <t>0.1174</t>
         </is>
       </c>
       <c r="AT243" t="inlineStr">
         <is>
-          <t>0.2973</t>
+          <t>0.2904</t>
         </is>
       </c>
       <c r="AU243" t="inlineStr">
         <is>
-          <t>70.52</t>
+          <t>72.34</t>
         </is>
       </c>
       <c r="AV243" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>24.03</t>
         </is>
       </c>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>40.56</t>
+          <t>35.38</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>18.78</t>
+          <t>20.95</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="AZ243" t="inlineStr">
         <is>
-          <t>0.1271</t>
+          <t>0.1474</t>
         </is>
       </c>
       <c r="BA243" t="inlineStr">
         <is>
-          <t>9.62</t>
+          <t>6.37</t>
         </is>
       </c>
       <c r="BB243" t="inlineStr">
         <is>
-          <t>42.91</t>
+          <t>32.86</t>
         </is>
       </c>
       <c r="BC243" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>86.45</t>
         </is>
       </c>
       <c r="BD243" t="inlineStr">
         <is>
-          <t>0.3912</t>
+          <t>0.3835</t>
         </is>
       </c>
       <c r="BE243" t="inlineStr">
         <is>
-          <t>0.1558</t>
+          <t>0.1341</t>
         </is>
       </c>
       <c r="BF243" t="inlineStr">
         <is>
-          <t>27.93</t>
+          <t>19.07</t>
         </is>
       </c>
       <c r="BG243" t="inlineStr"/>
@@ -66915,27 +66915,27 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>677649</t>
+          <t>665926</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Ezequiel Duran</t>
+          <t>Andres Gimenez</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>2026-08-05T00:05:00Z</t>
+          <t>2026-08-05T00:10:00Z</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
@@ -66945,17 +66945,17 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>Blade Tidwell</t>
+          <t>Hayden Wesneski</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>694918</t>
+          <t>669713</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
@@ -66978,26 +66978,26 @@
       </c>
       <c r="O244" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P244" t="n">
-        <v>20.3</v>
+        <v>7.2</v>
       </c>
       <c r="Q244" t="n">
-        <v>21.9</v>
+        <v>43</v>
       </c>
       <c r="R244" t="n">
         <v>27.6</v>
       </c>
       <c r="S244" t="n">
-        <v>59.8</v>
+        <v>47.9</v>
       </c>
       <c r="T244" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U244" t="n">
-        <v>42.3</v>
+        <v>7</v>
       </c>
       <c r="V244" t="inlineStr">
         <is>
@@ -67011,7 +67011,7 @@
       </c>
       <c r="X244" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y244" t="inlineStr">
@@ -67053,27 +67053,27 @@
       </c>
       <c r="AH244" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI244" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ244" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK244" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/25, 1 HR</t>
+          <t>Last 7 games: 3/18, 0 HR</t>
         </is>
       </c>
       <c r="AL244" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.4% barrel, 1.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 2.1 HR allowed</t>
         </is>
       </c>
       <c r="AM244" t="inlineStr">
@@ -67083,104 +67083,104 @@
       </c>
       <c r="AN244" t="inlineStr">
         <is>
-          <t>5.47</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="AO244" t="inlineStr">
         <is>
-          <t>33.91</t>
+          <t>24.41</t>
         </is>
       </c>
       <c r="AP244" t="inlineStr">
         <is>
-          <t>87.61</t>
+          <t>85.95</t>
         </is>
       </c>
       <c r="AQ244" t="inlineStr">
         <is>
-          <t>98.6051</t>
+          <t>95.761</t>
         </is>
       </c>
       <c r="AR244" t="inlineStr">
         <is>
-          <t>0.3608</t>
+          <t>0.3323</t>
         </is>
       </c>
       <c r="AS244" t="inlineStr">
         <is>
-          <t>0.1174</t>
+          <t>0.095</t>
         </is>
       </c>
       <c r="AT244" t="inlineStr">
         <is>
-          <t>0.2904</t>
+          <t>0.2793</t>
         </is>
       </c>
       <c r="AU244" t="inlineStr">
         <is>
-          <t>72.34</t>
+          <t>68.46</t>
         </is>
       </c>
       <c r="AV244" t="inlineStr">
         <is>
-          <t>24.03</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>35.38</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>20.95</t>
+          <t>23.02</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ244" t="inlineStr">
         <is>
-          <t>0.1474</t>
+          <t>0.1135</t>
         </is>
       </c>
       <c r="BA244" t="inlineStr">
         <is>
-          <t>6.37</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="BB244" t="inlineStr">
         <is>
-          <t>32.86</t>
+          <t>47.63</t>
         </is>
       </c>
       <c r="BC244" t="inlineStr">
         <is>
-          <t>86.45</t>
+          <t>90.19</t>
         </is>
       </c>
       <c r="BD244" t="inlineStr">
         <is>
-          <t>0.3835</t>
+          <t>0.4885</t>
         </is>
       </c>
       <c r="BE244" t="inlineStr">
         <is>
-          <t>0.1341</t>
+          <t>0.1501</t>
         </is>
       </c>
       <c r="BF244" t="inlineStr">
         <is>
-          <t>19.07</t>
+          <t>15.99</t>
         </is>
       </c>
       <c r="BG244" t="inlineStr"/>
       <c r="BH244" t="inlineStr"/>
       <c r="BI244" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ244" t="inlineStr"/>
@@ -67189,29 +67189,25 @@
       <c r="A245" t="n">
         <v>244</v>
       </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>665926</t>
-        </is>
-      </c>
+      <c r="B245" t="inlineStr"/>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Andres Gimenez</t>
+          <t>George Lombard</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>2026-08-05T00:10:00Z</t>
+          <t>2026-08-04T23:05:00Z</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
@@ -67226,12 +67222,12 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>Hayden Wesneski</t>
+          <t>Hunter Dobbins</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>669713</t>
+          <t>690928</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
@@ -67240,7 +67236,7 @@
         </is>
       </c>
       <c r="L245" t="n">
-        <v>31.1</v>
+        <v>30.8</v>
       </c>
       <c r="M245" t="inlineStr">
         <is>
@@ -67254,26 +67250,26 @@
       </c>
       <c r="O245" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P245" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="Q245" t="n">
-        <v>43</v>
+        <v>34.8</v>
       </c>
       <c r="R245" t="n">
-        <v>27.6</v>
+        <v>38.2</v>
       </c>
       <c r="S245" t="n">
         <v>47.9</v>
       </c>
       <c r="T245" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U245" t="n">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="V245" t="inlineStr">
         <is>
@@ -67312,7 +67308,7 @@
       </c>
       <c r="AC245" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H: P:2026/2025</t>
         </is>
       </c>
       <c r="AD245" t="inlineStr"/>
@@ -67322,34 +67318,18 @@
           <t>Direct BvP not yet weighted; 2026/2025 Statcast baseline active</t>
         </is>
       </c>
-      <c r="AG245" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AH245" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI245" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AJ245" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="AG245" t="inlineStr"/>
+      <c r="AH245" t="inlineStr"/>
+      <c r="AI245" t="inlineStr"/>
+      <c r="AJ245" t="inlineStr"/>
       <c r="AK245" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/18, 0 HR</t>
+          <t>Recent form unavailable</t>
         </is>
       </c>
       <c r="AL245" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.1% barrel, 2.1 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 7.0% barrel, 4.6 HR allowed</t>
         </is>
       </c>
       <c r="AM245" t="inlineStr">
@@ -67357,106 +67337,54 @@
           <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
-      <c r="AN245" t="inlineStr">
-        <is>
-          <t>3.49</t>
-        </is>
-      </c>
-      <c r="AO245" t="inlineStr">
-        <is>
-          <t>24.41</t>
-        </is>
-      </c>
-      <c r="AP245" t="inlineStr">
-        <is>
-          <t>85.95</t>
-        </is>
-      </c>
-      <c r="AQ245" t="inlineStr">
-        <is>
-          <t>95.761</t>
-        </is>
-      </c>
-      <c r="AR245" t="inlineStr">
-        <is>
-          <t>0.3323</t>
-        </is>
-      </c>
-      <c r="AS245" t="inlineStr">
-        <is>
-          <t>0.095</t>
-        </is>
-      </c>
-      <c r="AT245" t="inlineStr">
-        <is>
-          <t>0.2793</t>
-        </is>
-      </c>
-      <c r="AU245" t="inlineStr">
-        <is>
-          <t>68.46</t>
-        </is>
-      </c>
-      <c r="AV245" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AW245" t="inlineStr">
-        <is>
-          <t>38.1</t>
-        </is>
-      </c>
-      <c r="AX245" t="inlineStr">
-        <is>
-          <t>23.02</t>
-        </is>
-      </c>
-      <c r="AY245" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="AZ245" t="inlineStr">
-        <is>
-          <t>0.1135</t>
-        </is>
-      </c>
+      <c r="AN245" t="inlineStr"/>
+      <c r="AO245" t="inlineStr"/>
+      <c r="AP245" t="inlineStr"/>
+      <c r="AQ245" t="inlineStr"/>
+      <c r="AR245" t="inlineStr"/>
+      <c r="AS245" t="inlineStr"/>
+      <c r="AT245" t="inlineStr"/>
+      <c r="AU245" t="inlineStr"/>
+      <c r="AV245" t="inlineStr"/>
+      <c r="AW245" t="inlineStr"/>
+      <c r="AX245" t="inlineStr"/>
+      <c r="AY245" t="inlineStr"/>
+      <c r="AZ245" t="inlineStr"/>
       <c r="BA245" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="BB245" t="inlineStr">
         <is>
-          <t>47.63</t>
+          <t>43.59</t>
         </is>
       </c>
       <c r="BC245" t="inlineStr">
         <is>
-          <t>90.19</t>
+          <t>89.37</t>
         </is>
       </c>
       <c r="BD245" t="inlineStr">
         <is>
-          <t>0.4885</t>
+          <t>0.3842</t>
         </is>
       </c>
       <c r="BE245" t="inlineStr">
         <is>
-          <t>0.1501</t>
+          <t>0.1425</t>
         </is>
       </c>
       <c r="BF245" t="inlineStr">
         <is>
-          <t>15.99</t>
+          <t>22.88</t>
         </is>
       </c>
       <c r="BG245" t="inlineStr"/>
       <c r="BH245" t="inlineStr"/>
       <c r="BI245" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ245" t="inlineStr"/>

--- a/outputs/daily/hr_rankings_2026-08-04.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-04.xlsx
@@ -59584,7 +59584,7 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>34.8</v>
+        <v>35.1</v>
       </c>
       <c r="M217" t="inlineStr">
         <is>
@@ -59617,7 +59617,7 @@
         <v>50</v>
       </c>
       <c r="U217" t="n">
-        <v>39.7</v>
+        <v>45</v>
       </c>
       <c r="V217" t="inlineStr">
         <is>
@@ -59673,7 +59673,7 @@
       </c>
       <c r="AH217" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI217" t="inlineStr">
@@ -59688,7 +59688,7 @@
       </c>
       <c r="AK217" t="inlineStr">
         <is>
-          <t>Contact streak: 10/26 over last 7 games</t>
+          <t>Contact streak: 11/26 over last 7 games</t>
         </is>
       </c>
       <c r="AL217" t="inlineStr">
